--- a/meeple_back/src/main/resources/game-element/seed-card.xlsx
+++ b/meeple_back/src/main/resources/game-element/seed-card.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10119"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/biggie/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D5C50C-658A-9A44-B021-44FA99A817AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="44220" windowHeight="26720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="8670"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$B$1:$J$27</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,9 +29,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="68">
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -91,9 +87,6 @@
   </si>
   <si>
     <t>baseUsageFee</t>
-  </si>
-  <si>
-    <t>number</t>
   </si>
   <si>
     <t>땅</t>
@@ -251,23 +244,31 @@
     <t>게자리는 황도12궁의 4번째 별자리로 프톨레마이오스의 별자리 중 하나이기도 하다. 고대에는 하지점이 게자리에 있어, 북회귀선을 ‘게자리 회귀선’이라고 불렀지만 지금은 이동하여 쌍둥이자리에 있다.
 프톨레마이오스의 별자리 : 2세기 그리스 천문학자 프톨레마이오스의 저서 알마게스트에 수록된 48개의 별자리</t>
   </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -331,7 +332,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -608,12 +609,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
     <col min="5" max="5" width="47.5" bestFit="1" customWidth="1"/>
@@ -624,39 +624,39 @@
     <col min="10" max="10" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -664,16 +664,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3">
         <v>10</v>
@@ -688,24 +688,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3">
         <v>15</v>
@@ -720,24 +720,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
         <v>4</v>
       </c>
-      <c r="B4" s="3">
-        <v>3</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3">
         <v>30</v>
@@ -752,24 +752,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="128" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="119" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
         <v>5</v>
       </c>
-      <c r="B5" s="3">
-        <v>4</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3">
         <v>50</v>
@@ -784,24 +784,24 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
-        <v>5</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3">
         <v>30</v>
@@ -816,24 +816,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
         <v>8</v>
       </c>
-      <c r="B7" s="3">
-        <v>6</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3">
         <v>15</v>
@@ -848,24 +848,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
         <v>9</v>
       </c>
-      <c r="B8" s="3">
-        <v>7</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3">
         <v>15</v>
@@ -880,24 +880,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
         <v>11</v>
       </c>
-      <c r="B9" s="3">
-        <v>8</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3">
         <v>25</v>
@@ -912,24 +912,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
         <v>12</v>
       </c>
-      <c r="B10" s="3">
-        <v>9</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" s="3">
         <v>30</v>
@@ -944,24 +944,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="119" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
         <v>14</v>
       </c>
-      <c r="B11" s="3">
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="G11" s="3">
         <v>40</v>
@@ -976,24 +976,24 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
-        <v>11</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" s="3">
         <v>45</v>
@@ -1008,24 +1008,24 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="119" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
         <v>18</v>
       </c>
-      <c r="B13" s="3">
-        <v>12</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="3">
         <v>50</v>
@@ -1040,24 +1040,24 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
         <v>19</v>
       </c>
-      <c r="B14" s="3">
-        <v>13</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" s="3">
         <v>60</v>
@@ -1072,24 +1072,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="119" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
         <v>21</v>
       </c>
-      <c r="B15" s="3">
-        <v>14</v>
-      </c>
       <c r="C15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="G15" s="3">
         <v>60</v>
@@ -1104,24 +1104,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
         <v>22</v>
       </c>
-      <c r="B16" s="3">
-        <v>15</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G16" s="3">
         <v>50</v>
@@ -1136,24 +1136,24 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
         <v>24</v>
       </c>
-      <c r="B17" s="3">
-        <v>16</v>
-      </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G17" s="3">
         <v>45</v>
@@ -1168,24 +1168,24 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="128" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="119" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
         <v>25</v>
       </c>
-      <c r="B18" s="3">
-        <v>17</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="3">
         <v>50</v>
@@ -1200,24 +1200,24 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="119" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
         <v>26</v>
       </c>
-      <c r="B19" s="3">
-        <v>18</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3">
         <v>40</v>
@@ -1232,24 +1232,24 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="128" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="136" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
         <v>27</v>
       </c>
-      <c r="B20" s="3">
-        <v>19</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3">
         <v>30</v>
@@ -1264,24 +1264,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
         <v>28</v>
       </c>
-      <c r="B21" s="3">
-        <v>20</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3">
         <v>25</v>
@@ -1296,24 +1296,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
         <v>31</v>
       </c>
-      <c r="B22" s="3">
-        <v>21</v>
-      </c>
       <c r="C22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G22" s="3">
         <v>30</v>
@@ -1328,24 +1328,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
         <v>32</v>
       </c>
-      <c r="B23" s="3">
-        <v>22</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G23" s="3">
         <v>40</v>
@@ -1360,24 +1360,24 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
         <v>34</v>
       </c>
-      <c r="B24" s="3">
-        <v>23</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G24" s="3">
         <v>40</v>
@@ -1392,24 +1392,24 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3">
         <v>36</v>
       </c>
-      <c r="B25" s="3">
-        <v>24</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G25" s="3">
         <v>30</v>
@@ -1424,24 +1424,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3">
         <v>38</v>
       </c>
-      <c r="B26" s="3">
-        <v>25</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="3">
         <v>10</v>
@@ -1456,24 +1456,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="102" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3">
         <v>39</v>
       </c>
-      <c r="B27" s="3">
-        <v>26</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3">
         <v>10</v>

--- a/meeple_back/src/main/resources/game-element/seed-card.xlsx
+++ b/meeple_back/src/main/resources/game-element/seed-card.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10119"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/biggie/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E9C556-8218-1B4C-939E-58989F8B8063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="8670"/>
+    <workbookView xWindow="32920" yWindow="9400" windowWidth="21980" windowHeight="21800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -256,19 +257,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -317,7 +318,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -330,9 +331,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -609,9 +613,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -624,7 +628,7 @@
     <col min="10" max="10" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
@@ -656,7 +660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -675,20 +679,21 @@
       <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="3">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3">
-        <v>5</v>
-      </c>
-      <c r="I2" s="3">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G2" s="4">
+        <v>100000</v>
+      </c>
+      <c r="H2" s="4">
+        <v>50000</v>
+      </c>
+      <c r="I2" s="4">
+        <v>50000</v>
+      </c>
+      <c r="J2" s="4">
+        <v>200000</v>
+      </c>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -707,20 +712,20 @@
       <c r="F3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
-        <v>15</v>
-      </c>
-      <c r="H3" s="3">
-        <v>8</v>
-      </c>
-      <c r="I3" s="3">
-        <v>10</v>
-      </c>
-      <c r="J3" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G3" s="4">
+        <v>150000</v>
+      </c>
+      <c r="H3" s="4">
+        <v>80000</v>
+      </c>
+      <c r="I3" s="4">
+        <v>100000</v>
+      </c>
+      <c r="J3" s="4">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -739,20 +744,20 @@
       <c r="F4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="3">
-        <v>30</v>
-      </c>
-      <c r="H4" s="3">
-        <v>15</v>
-      </c>
-      <c r="I4" s="3">
-        <v>20</v>
-      </c>
-      <c r="J4" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="119" x14ac:dyDescent="0.45">
+      <c r="G4" s="4">
+        <v>300000</v>
+      </c>
+      <c r="H4" s="4">
+        <v>150000</v>
+      </c>
+      <c r="I4" s="4">
+        <v>200000</v>
+      </c>
+      <c r="J4" s="4">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="128" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -771,20 +776,20 @@
       <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="3">
-        <v>50</v>
-      </c>
-      <c r="H5" s="3">
-        <v>25</v>
-      </c>
-      <c r="I5" s="3">
-        <v>35</v>
-      </c>
-      <c r="J5" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G5" s="4">
+        <v>500000</v>
+      </c>
+      <c r="H5" s="4">
+        <v>250000</v>
+      </c>
+      <c r="I5" s="4">
+        <v>350000</v>
+      </c>
+      <c r="J5" s="4">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -803,20 +808,20 @@
       <c r="F6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="3">
-        <v>30</v>
-      </c>
-      <c r="H6" s="3">
-        <v>15</v>
-      </c>
-      <c r="I6" s="3">
-        <v>20</v>
-      </c>
-      <c r="J6" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G6" s="4">
+        <v>300000</v>
+      </c>
+      <c r="H6" s="4">
+        <v>150000</v>
+      </c>
+      <c r="I6" s="4">
+        <v>200000</v>
+      </c>
+      <c r="J6" s="4">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -835,20 +840,20 @@
       <c r="F7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="3">
-        <v>15</v>
-      </c>
-      <c r="H7" s="3">
-        <v>8</v>
-      </c>
-      <c r="I7" s="3">
-        <v>10</v>
-      </c>
-      <c r="J7" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G7" s="4">
+        <v>150000</v>
+      </c>
+      <c r="H7" s="4">
+        <v>80000</v>
+      </c>
+      <c r="I7" s="4">
+        <v>100000</v>
+      </c>
+      <c r="J7" s="4">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -867,20 +872,20 @@
       <c r="F8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="3">
-        <v>15</v>
-      </c>
-      <c r="H8" s="3">
-        <v>8</v>
-      </c>
-      <c r="I8" s="3">
-        <v>10</v>
-      </c>
-      <c r="J8" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G8" s="4">
+        <v>150000</v>
+      </c>
+      <c r="H8" s="4">
+        <v>80000</v>
+      </c>
+      <c r="I8" s="4">
+        <v>100000</v>
+      </c>
+      <c r="J8" s="4">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -899,20 +904,20 @@
       <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="3">
-        <v>25</v>
-      </c>
-      <c r="H9" s="3">
-        <v>13</v>
-      </c>
-      <c r="I9" s="3">
-        <v>16</v>
-      </c>
-      <c r="J9" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G9" s="4">
+        <v>250000</v>
+      </c>
+      <c r="H9" s="4">
+        <v>130000</v>
+      </c>
+      <c r="I9" s="4">
+        <v>160000</v>
+      </c>
+      <c r="J9" s="4">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -931,20 +936,20 @@
       <c r="F10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="3">
-        <v>30</v>
-      </c>
-      <c r="H10" s="3">
-        <v>15</v>
-      </c>
-      <c r="I10" s="3">
-        <v>20</v>
-      </c>
-      <c r="J10" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="119" x14ac:dyDescent="0.45">
+      <c r="G10" s="4">
+        <v>300000</v>
+      </c>
+      <c r="H10" s="4">
+        <v>150000</v>
+      </c>
+      <c r="I10" s="4">
+        <v>200000</v>
+      </c>
+      <c r="J10" s="4">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -963,20 +968,20 @@
       <c r="F11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="3">
-        <v>40</v>
-      </c>
-      <c r="H11" s="3">
-        <v>20</v>
-      </c>
-      <c r="I11" s="3">
-        <v>27</v>
-      </c>
-      <c r="J11" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G11" s="4">
+        <v>400000</v>
+      </c>
+      <c r="H11" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I11" s="4">
+        <v>270000</v>
+      </c>
+      <c r="J11" s="4">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -995,20 +1000,20 @@
       <c r="F12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="3">
-        <v>45</v>
-      </c>
-      <c r="H12" s="3">
-        <v>23</v>
-      </c>
-      <c r="I12" s="3">
-        <v>30</v>
-      </c>
-      <c r="J12" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="119" x14ac:dyDescent="0.45">
+      <c r="G12" s="4">
+        <v>450000</v>
+      </c>
+      <c r="H12" s="4">
+        <v>230000</v>
+      </c>
+      <c r="I12" s="4">
+        <v>300000</v>
+      </c>
+      <c r="J12" s="4">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1027,20 +1032,20 @@
       <c r="F13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="3">
-        <v>50</v>
-      </c>
-      <c r="H13" s="3">
-        <v>25</v>
-      </c>
-      <c r="I13" s="3">
-        <v>35</v>
-      </c>
-      <c r="J13" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G13" s="4">
+        <v>500000</v>
+      </c>
+      <c r="H13" s="4">
+        <v>250000</v>
+      </c>
+      <c r="I13" s="4">
+        <v>350000</v>
+      </c>
+      <c r="J13" s="4">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1059,20 +1064,20 @@
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
-        <v>60</v>
-      </c>
-      <c r="H14" s="3">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3">
-        <v>40</v>
-      </c>
-      <c r="J14" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="119" x14ac:dyDescent="0.45">
+      <c r="G14" s="4">
+        <v>600000</v>
+      </c>
+      <c r="H14" s="4">
+        <v>300000</v>
+      </c>
+      <c r="I14" s="4">
+        <v>400000</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1091,20 +1096,20 @@
       <c r="F15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="3">
-        <v>60</v>
-      </c>
-      <c r="H15" s="3">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3">
-        <v>40</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G15" s="4">
+        <v>600000</v>
+      </c>
+      <c r="H15" s="4">
+        <v>300000</v>
+      </c>
+      <c r="I15" s="4">
+        <v>400000</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1123,20 +1128,20 @@
       <c r="F16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="3">
-        <v>50</v>
-      </c>
-      <c r="H16" s="3">
-        <v>25</v>
-      </c>
-      <c r="I16" s="3">
-        <v>35</v>
-      </c>
-      <c r="J16" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G16" s="4">
+        <v>500000</v>
+      </c>
+      <c r="H16" s="4">
+        <v>250000</v>
+      </c>
+      <c r="I16" s="4">
+        <v>350000</v>
+      </c>
+      <c r="J16" s="4">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1155,20 +1160,20 @@
       <c r="F17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="3">
-        <v>45</v>
-      </c>
-      <c r="H17" s="3">
-        <v>23</v>
-      </c>
-      <c r="I17" s="3">
-        <v>30</v>
-      </c>
-      <c r="J17" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="119" x14ac:dyDescent="0.45">
+      <c r="G17" s="4">
+        <v>450000</v>
+      </c>
+      <c r="H17" s="4">
+        <v>230000</v>
+      </c>
+      <c r="I17" s="4">
+        <v>300000</v>
+      </c>
+      <c r="J17" s="4">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="128" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1187,20 +1192,20 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="3">
-        <v>50</v>
-      </c>
-      <c r="H18" s="3">
-        <v>25</v>
-      </c>
-      <c r="I18" s="3">
-        <v>35</v>
-      </c>
-      <c r="J18" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="119" x14ac:dyDescent="0.45">
+      <c r="G18" s="4">
+        <v>500000</v>
+      </c>
+      <c r="H18" s="4">
+        <v>250000</v>
+      </c>
+      <c r="I18" s="4">
+        <v>350000</v>
+      </c>
+      <c r="J18" s="4">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="112" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1219,20 +1224,20 @@
       <c r="F19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="3">
-        <v>40</v>
-      </c>
-      <c r="H19" s="3">
-        <v>20</v>
-      </c>
-      <c r="I19" s="3">
-        <v>27</v>
-      </c>
-      <c r="J19" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="136" x14ac:dyDescent="0.45">
+      <c r="G19" s="4">
+        <v>400000</v>
+      </c>
+      <c r="H19" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I19" s="4">
+        <v>270000</v>
+      </c>
+      <c r="J19" s="4">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="128" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1251,20 +1256,20 @@
       <c r="F20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="3">
-        <v>30</v>
-      </c>
-      <c r="H20" s="3">
-        <v>15</v>
-      </c>
-      <c r="I20" s="3">
-        <v>20</v>
-      </c>
-      <c r="J20" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G20" s="4">
+        <v>300000</v>
+      </c>
+      <c r="H20" s="4">
+        <v>150000</v>
+      </c>
+      <c r="I20" s="4">
+        <v>200000</v>
+      </c>
+      <c r="J20" s="4">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1283,20 +1288,20 @@
       <c r="F21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="3">
-        <v>25</v>
-      </c>
-      <c r="H21" s="3">
-        <v>13</v>
-      </c>
-      <c r="I21" s="3">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G21" s="4">
+        <v>250000</v>
+      </c>
+      <c r="H21" s="4">
+        <v>130000</v>
+      </c>
+      <c r="I21" s="4">
+        <v>160000</v>
+      </c>
+      <c r="J21" s="4">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1315,20 +1320,20 @@
       <c r="F22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="3">
-        <v>30</v>
-      </c>
-      <c r="H22" s="3">
-        <v>15</v>
-      </c>
-      <c r="I22" s="3">
-        <v>15</v>
-      </c>
-      <c r="J22" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G22" s="4">
+        <v>300000</v>
+      </c>
+      <c r="H22" s="4">
+        <v>150000</v>
+      </c>
+      <c r="I22" s="4">
+        <v>150000</v>
+      </c>
+      <c r="J22" s="4">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1347,20 +1352,20 @@
       <c r="F23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="3">
-        <v>40</v>
-      </c>
-      <c r="H23" s="3">
-        <v>20</v>
-      </c>
-      <c r="I23" s="3">
-        <v>27</v>
-      </c>
-      <c r="J23" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G23" s="4">
+        <v>400000</v>
+      </c>
+      <c r="H23" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I23" s="4">
+        <v>270000</v>
+      </c>
+      <c r="J23" s="4">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="112" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1379,20 +1384,20 @@
       <c r="F24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="3">
-        <v>40</v>
-      </c>
-      <c r="H24" s="3">
-        <v>20</v>
-      </c>
-      <c r="I24" s="3">
-        <v>27</v>
-      </c>
-      <c r="J24" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G24" s="4">
+        <v>400000</v>
+      </c>
+      <c r="H24" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I24" s="4">
+        <v>270000</v>
+      </c>
+      <c r="J24" s="4">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="112" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1411,20 +1416,20 @@
       <c r="F25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G25" s="3">
-        <v>30</v>
-      </c>
-      <c r="H25" s="3">
-        <v>15</v>
-      </c>
-      <c r="I25" s="3">
-        <v>15</v>
-      </c>
-      <c r="J25" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G25" s="4">
+        <v>300000</v>
+      </c>
+      <c r="H25" s="4">
+        <v>150000</v>
+      </c>
+      <c r="I25" s="4">
+        <v>150000</v>
+      </c>
+      <c r="J25" s="4">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1443,20 +1448,20 @@
       <c r="F26" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G26" s="3">
-        <v>10</v>
-      </c>
-      <c r="H26" s="3">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="G26" s="4">
+        <v>100000</v>
+      </c>
+      <c r="H26" s="4">
+        <v>50000</v>
+      </c>
+      <c r="I26" s="4">
+        <v>50000</v>
+      </c>
+      <c r="J26" s="4">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1475,17 +1480,17 @@
       <c r="F27" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G27" s="3">
-        <v>10</v>
-      </c>
-      <c r="H27" s="3">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
-        <v>20</v>
+      <c r="G27" s="4">
+        <v>100000</v>
+      </c>
+      <c r="H27" s="4">
+        <v>50000</v>
+      </c>
+      <c r="I27" s="4">
+        <v>50000</v>
+      </c>
+      <c r="J27" s="4">
+        <v>200000</v>
       </c>
     </row>
   </sheetData>
